--- a/red_duke_demo/output/Client_Audit_Checklist.xlsx
+++ b/red_duke_demo/output/Client_Audit_Checklist.xlsx
@@ -551,15 +551,15 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>ABC Corporation - High-Level Critical Path Project Plan.docx
-ABC Corporation 25080 BRD v0.1.docx
-Implementation_Documentation_Standardization_Capstone_Scope.docx</t>
+          <t>Implementation_Documentation_Standardization_Capstone_Scope.docx
+ABC Corporation - High-Level Critical Path Project Plan.docx
+ABC Corporation 25080 BRD v0.1.docx</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>"sts relevant artifacts (e.g., brds, plans, diagrams, status notes) and produces clear client"
-"siness requirements document (brd) is to capture the detailed requirements aligning with the"</t>
+          <t>"siness requirements document (brd) is to capture the detailed requirements aligning with the"
+"plan) (10 days can overlap w/brd) brd sessions (outcome - approved requirements for implemen"</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -602,8 +602,8 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>"sessions (outcome - executive project plan) (10 days can overlap w/brd) brd sessions (outcome - approv"
-", data integrity, or expected timelines. abc corporations may define custom rules and thresholds f"</t>
+          <t>", data integrity, or expected timelines. abc corporations may define custom rules and thresholds f"
+"sessions (outcome - executive project plan) (10 days can overlap w/brd) brd sessions (outcome - approv"</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -682,16 +682,16 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>ABC Corporation - High-Level Critical Path Project Plan.docx
-ABC Corporation 25080 BRD v0.1.docx
+          <t>ABC Corporation 25080 BRD v0.1.docx
 Implementation_Documentation_Standardization_Capstone_Scope.docx
+ABC Corporation - High-Level Critical Path Project Plan.docx
 ABC Corporation -WF Diagram.vsdx</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>"ugh advanced technologies and workflow automation.  ## service delivery model &amp; business hours sds"
-"n – scanner, sftp, email fax, workflow etc.  (20 days) client access, reporting requirement and sl"</t>
+          <t>"───────────────────────────── workflow page 1 ────────────────────────────────────────   [image im"
+"ugh advanced technologies and workflow automation.  ## service delivery model &amp; business hours sds"</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -728,9 +728,9 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>ABC Corporation - High-Level Critical Path Project Plan.docx
-ABC Corporation 25080 BRD v0.1.docx
-Implementation_Documentation_Standardization_Capstone_Scope.docx</t>
+          <t>Implementation_Documentation_Standardization_Capstone_Scope.docx
+ABC Corporation - High-Level Critical Path Project Plan.docx
+ABC Corporation 25080 BRD v0.1.docx</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -773,15 +773,15 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>ABC Corporation - High-Level Critical Path Project Plan.docx
-ABC Corporation 25080 BRD v0.1.docx
-Implementation_Documentation_Standardization_Capstone_Scope.docx</t>
+          <t>Implementation_Documentation_Standardization_Capstone_Scope.docx
+ABC Corporation - High-Level Critical Path Project Plan.docx
+ABC Corporation 25080 BRD v0.1.docx</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>"w overviews, and ‘known gaps’ reports that can be used by implementation, pm, engineering, and c"
-"ough exception monitoring and reported to the abc corporation for correction and resubmission. e"</t>
+          <t>"tc.  (20 days) client access, reporting requirement and sla (10 days can overlap with technical"
+"w overviews, and ‘known gaps’ reports that can be used by implementation, pm, engineering, and c"</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,15 +818,15 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>ABC Corporation - High-Level Critical Path Project Plan.docx
-ABC Corporation 25080 BRD v0.1.docx
-Implementation_Documentation_Standardization_Capstone_Scope.docx</t>
+          <t>Implementation_Documentation_Standardization_Capstone_Scope.docx
+ABC Corporation - High-Level Critical Path Project Plan.docx
+ABC Corporation 25080 BRD v0.1.docx</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>"h prompts, templates, and evaluation criteria to measure documentation accuracy, usefulness,"
-"s, and lay the groundwork for testing and validation. prompt delivery and review of these materia"</t>
+          <t>"s, and lay the groundwork for testing and validation. prompt delivery and review of these materia"
+"h prompts, templates, and evaluation criteria to measure documentation accuracy, usefulness,"</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -863,9 +863,9 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>ABC Corporation - High-Level Critical Path Project Plan.docx
-ABC Corporation 25080 BRD v0.1.docx
+          <t>ABC Corporation 25080 BRD v0.1.docx
 Implementation_Documentation_Standardization_Capstone_Scope.docx
+ABC Corporation - High-Level Critical Path Project Plan.docx
 ABC Corporation -WF Diagram.vsdx</t>
         </is>
       </c>
@@ -909,8 +909,8 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>ABC Corporation - High-Level Critical Path Project Plan.docx
-ABC Corporation 25080 BRD v0.1.docx
+          <t>ABC Corporation 25080 BRD v0.1.docx
+ABC Corporation - High-Level Critical Path Project Plan.docx
 ABC Corporation -WF Diagram.vsdx</t>
         </is>
       </c>
@@ -998,15 +998,15 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>ABC Corporation - High-Level Critical Path Project Plan.docx
-ABC Corporation 25080 BRD v0.1.docx
-Implementation_Documentation_Standardization_Capstone_Scope.docx</t>
+          <t>Implementation_Documentation_Standardization_Capstone_Scope.docx
+ABC Corporation - High-Level Critical Path Project Plan.docx
+ABC Corporation 25080 BRD v0.1.docx</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>"efficiency, ensure regulatory compliance, and enhance data accuracy through advanced technologies an"
-"decisions (rad), and evidence checklist. creation of reusable prompt sets, document templates, and"</t>
+          <t>"decisions (rad), and evidence checklist. creation of reusable prompt sets, document templates, and"
+"10/15) operational readiness checklist review (5 days) mr review and code/configuration deployment"</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">

--- a/red_duke_demo/output/Client_Audit_Checklist.xlsx
+++ b/red_duke_demo/output/Client_Audit_Checklist.xlsx
@@ -551,15 +551,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Implementation_Documentation_Standardization_Capstone_Scope.docx
-ABC Corporation - High-Level Critical Path Project Plan.docx
-ABC Corporation 25080 BRD v0.1.docx</t>
+          <t>MY_Insurance_25082_BRD_v0_1.docx</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>"siness requirements document (brd) is to capture the detailed requirements aligning with the"
-"plan) (10 days can overlap w/brd) brd sessions (outcome - approved requirements for implemen"</t>
+          <t>"my_insurance_25082_brd_v0_1.docx"</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -589,21 +586,19 @@
           <t>SOC2</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>FOUND</t>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>ABC Corporation - High-Level Critical Path Project Plan.docx
-ABC Corporation 25080 BRD v0.1.docx</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>", data integrity, or expected timelines. abc corporations may define custom rules and thresholds f"
-"sessions (outcome - executive project plan) (10 days can overlap w/brd) brd sessions (outcome - approv"</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -675,23 +670,19 @@
           <t>HITRUST</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>FOUND</t>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>ABC Corporation 25080 BRD v0.1.docx
-Implementation_Documentation_Standardization_Capstone_Scope.docx
-ABC Corporation - High-Level Critical Path Project Plan.docx
-ABC Corporation -WF Diagram.vsdx</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>"───────────────────────────── workflow page 1 ────────────────────────────────────────   [image im"
-"ugh advanced technologies and workflow automation.  ## service delivery model &amp; business hours sds"</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -721,22 +712,19 @@
           <t>HITRUST / SOC2</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>FOUND</t>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Implementation_Documentation_Standardization_Capstone_Scope.docx
-ABC Corporation - High-Level Critical Path Project Plan.docx
-ABC Corporation 25080 BRD v0.1.docx</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>"oring in production (30 days) transition to support team (5 days) abc corporation - high-level criti"
-"mable documentation of client implementations by leveraging existing artifacts stored in sharepoint. rat"</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -766,22 +754,19 @@
           <t>SOC2</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>FOUND</t>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Implementation_Documentation_Standardization_Capstone_Scope.docx
-ABC Corporation - High-Level Critical Path Project Plan.docx
-ABC Corporation 25080 BRD v0.1.docx</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>"tc.  (20 days) client access, reporting requirement and sla (10 days can overlap with technical"
-"w overviews, and ‘known gaps’ reports that can be used by implementation, pm, engineering, and c"</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -811,22 +796,19 @@
           <t>HITRUST</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>FOUND</t>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Implementation_Documentation_Standardization_Capstone_Scope.docx
-ABC Corporation - High-Level Critical Path Project Plan.docx
-ABC Corporation 25080 BRD v0.1.docx</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>"s, and lay the groundwork for testing and validation. prompt delivery and review of these materia"
-"h prompts, templates, and evaluation criteria to measure documentation accuracy, usefulness,"</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -856,23 +838,19 @@
           <t>HITRUST</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>FOUND</t>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>ABC Corporation 25080 BRD v0.1.docx
-Implementation_Documentation_Standardization_Capstone_Scope.docx
-ABC Corporation - High-Level Critical Path Project Plan.docx
-ABC Corporation -WF Diagram.vsdx</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>"pt third-party tools ran into security/process hurdles and did not yield durable change. sds needs"
-"lds are used to validate and associate incoming documents with an active member record, suppo"</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -902,22 +880,19 @@
           <t>SOC2</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>FOUND</t>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>ABC Corporation 25080 BRD v0.1.docx
-ABC Corporation - High-Level Critical Path Project Plan.docx
-ABC Corporation -WF Diagram.vsdx</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>"e import]   [data capture]   [eligibility matching]   [match]   [reject letter]   [fail]   [original"
-"on) functional testing of non-claims (5 days) volume testing (15 –20 days) uat by client (10 da"</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -947,21 +922,19 @@
           <t>HITRUST / SOC2</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>FOUND</t>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>ABC Corporation - High-Level Critical Path Project Plan.docx
-ABC Corporation 25080 BRD v0.1.docx</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>"by client (10 days) deploy / warranty (8/18 - 10/15) operational readiness checklist review (5 da"
-"hing queue during the initial warranty period of all implementations. this ensures early detection"</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -991,22 +964,19 @@
           <t>HITRUST</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>FOUND</t>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Implementation_Documentation_Standardization_Capstone_Scope.docx
-ABC Corporation - High-Level Critical Path Project Plan.docx
-ABC Corporation 25080 BRD v0.1.docx</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>"decisions (rad), and evidence checklist. creation of reusable prompt sets, document templates, and"
-"10/15) operational readiness checklist review (5 days) mr review and code/configuration deployment"</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1068,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1120,7 +1090,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>ABC Corporation - High-Level Critical Path Project Plan.docx</t>
+          <t>MY_Insurance_-_High-Level_Critical_Path_Project_Plan.docx</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
@@ -1130,12 +1100,12 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>786.2</t>
+          <t>775.1</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
@@ -1157,27 +1127,27 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>ABC Corporation -WF Diagram.vsdx</t>
+          <t>MY_Insurance_25082_BRD_v0_1.docx</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Visio Diagram (.vsdx)</t>
+          <t>Word Document (.docx)</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>184.2</t>
+          <t>182.4</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -1186,80 +1156,6 @@
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>ABC Corporation 25080 BRD v0.1.docx</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Word Document (.docx)</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>305.3</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>5729</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Implementation_Documentation_Standardization_Capstone_Scope.docx</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Word Document (.docx)</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>37.1</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>579</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1276,7 +1172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1310,7 +1206,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Client Kickoff / Scope Presentation</t>
+          <t>High-Level Project Plan / Critical Path</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
@@ -1325,27 +1221,225 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>Obtain client kickoff / scope presentation from PM before Initiation (TG-1) gate.</t>
+          <t>Obtain high-level project plan / critical path from PM before Initiation (TG-1) gate.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
+          <t>Client Kickoff / Scope Presentation</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Initiation (TG-1)</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Obtain client kickoff / scope presentation from PM before Initiation (TG-1) gate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Workflow Diagram / Process Flow</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Design (TG0)</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Obtain workflow diagram / process flow from Engineering before Design (TG0) gate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Implementation / Transition Workbook</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Implementation (TG1)</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Obtain implementation / transition workbook from PM / Engineering before Implementation (TG1) gate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Reporting Requirements &amp; SLA Documentation</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Implementation (TG1)</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Obtain reporting requirements &amp; sla documentation from PM before Implementation (TG1) gate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Testing Evidence / UAT Sign-off</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Test (TG2)</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Obtain testing evidence / uat sign-off from Engineering before Test (TG2) gate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Security &amp; Access Control Documentation</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Initiation (TG-1)</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Obtain security &amp; access control documentation from Engineering before Initiation (TG-1) gate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Eligibility / Claims Configuration</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Implementation (TG1)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Obtain eligibility / claims configuration from Engineering before Implementation (TG1) gate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>M2P / Go-Live Sign-off</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Deploy/Warranty (TG3)</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Obtain m2p / go-live sign-off from PM / Tech Lead before Deploy/Warranty (TG3) gate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>TPM / Compliance Checklist</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Test (TG2)</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Obtain tpm / compliance checklist from PM / Engineer before Test (TG2) gate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
           <t>Training &amp; Process Awareness Documentation</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Initiation (TG-1)</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Obtain training &amp; process awareness documentation from PM before Initiation (TG-1) gate.</t>
         </is>
